--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/embedded-rtos-medium.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/embedded-rtos-medium.xlsx
@@ -460,19 +460,19 @@
         <v>Mutex (Mutual Exclusion) dùng để bảo vệ tài nguyên dùng chung (Shared Resource). Nó có cơ chế "mượn khóa" (Ownership). Chỉ task đang giữ Mutex mới giải phóng được nó. Semaphore dùng để đồng bộ hóa (signaling): Task A tạo ra sự kiện thì nhả semaphore để Task B nhận và chạy.</v>
       </c>
       <c r="F2" t="str">
-        <v>Mutex có khái niệm sở hữu (Ownership - chỉ task khóa mới được mở) và hỗ trợ giải quyết Priority Inversion; Binary Semaphore không có owner, chuyên dùng cho signaling — sở hữu &amp; chống nghịch đảo ưu tiên vs phát tín hiệu</v>
+        <v>Mutex bắt buộc phải lưu trong bộ nhớ Flash; còn Binary Semaphore lưu trong bộ nhớ RAM — phân loại phân vùng bộ nhớ</v>
       </c>
       <c r="G2" t="str">
         <v>Mutex chỉ dùng cho lập trình nhúng 32-bit; Binary Semaphore chỉ dùng cho lập trình nhúng 8-bit — phân loại theo bit vi điều khiển</v>
       </c>
       <c r="H2" t="str">
-        <v>Mutex bắt buộc phải lưu trong bộ nhớ Flash; còn Binary Semaphore lưu trong bộ nhớ RAM — phân loại phân vùng bộ nhớ</v>
+        <v>Mutex có khái niệm sở hữu (Ownership - chỉ task khóa mới được mở) và hỗ trợ giải quyết Priority Inversion; Binary Semaphore không có owner, chuyên dùng cho signaling — sở hữu &amp; chống nghịch đảo ưu tiên vs phát tín hiệu</v>
       </c>
       <c r="I2" t="str">
         <v>Mutex chạy nhanh gấp 10 lần so với Binary Semaphore do không sử dụng cơ chế hàng đợi — so sánh hiệu năng chạy</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>Priority Inversion là lỗi thiết kế kinh điển (từng làm tê liệt robot tự hành Mars Pathfinder). Task Cao bị chặn bởi Task Thấp (do dùng chung khóa). Nhưng Task Trung bình không cần khóa lại nhảy vào cướp CPU của Task Thấp, làm Task Thấp không thể chạy để trả khóa cho Task Cao, gián tiếp làm Task Cao bị block lâu hơn cả Task Trung bình.</v>
       </c>
       <c r="F3" t="str">
+        <v>Vi điều khiển bị quá nhiệt khiến hệ điều hành hoạt động sai lệch logic lập lịch — vi điều khiển quá nhiệt</v>
+      </c>
+      <c r="G3" t="str">
         <v>Task độ ưu tiên cao bị block để đợi tài nguyên giữ bởi task độ ưu tiên thấp, trong khi một task độ ưu tiên trung bình nhảy vào chiếm CPU cản trở task thấp nhả tài nguyên — task trung bình cản trở task cao</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>Hệ điều hành tự động đảo ngược độ ưu tiên của tất cả các task sau mỗi 10 mili-giây — tự động đảo độ ưu tiên</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>Lập trình viên vô ý khai báo sai số thứ tự độ ưu tiên của các task trong hàm main() — lỗi khai báo nhầm lẫn</v>
       </c>
-      <c r="I3" t="str">
-        <v>Vi điều khiển bị quá nhiệt khiến hệ điều hành hoạt động sai lệch logic lập lịch — vi điều khiển quá nhiệt</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -524,19 +524,19 @@
         <v>Khi nâng tạm thời priority của Task Thấp lên bằng Task Cao, các Task Trung bình sẽ không thể cướp CPU của nó được nữa. Task Thấp sẽ nhanh chóng hoàn thành vùng găng (Critical Section) để nhả Mutex cho Task Cao.</v>
       </c>
       <c r="F4" t="str">
+        <v>Ngắt toàn bộ các yêu cầu xử lý của CPU để tập trung chạy lại từ đầu hệ điều hành — reset hệ điều hành</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Tạo ra một bản sao khóa phụ để cấp phát cho Task cao cùng sử dụng chung tài nguyên — tạo khóa phụ song song</v>
+      </c>
+      <c r="H4" t="str">
         <v>Tạm thời nâng độ ưu tiên của Task thấp (đang giữ khóa) lên bằng độ ưu tiên của Task cao (đang đợi khóa) để nó chạy nhanh và trả khóa, sau đó trả về độ ưu tiên cũ — nâng ưu tiên tạm thời để trả khóa</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>Tự động xóa bỏ Task trung bình ra khỏi bộ nhớ của hệ thống khi có tranh chấp xảy ra — xóa task trung bình</v>
       </c>
-      <c r="H4" t="str">
-        <v>Tạo ra một bản sao khóa phụ để cấp phát cho Task cao cùng sử dụng chung tài nguyên — tạo khóa phụ song song</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Ngắt toàn bộ các yêu cầu xử lý của CPU để tập trung chạy lại từ đầu hệ điều hành — reset hệ điều hành</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>ISR cần thực thi cực nhanh và không được phép bị chặn (Blocked). Các API RTOS thông thường có cơ chế block/timeout nếu tài nguyên chưa sẵn sàng. Phiên bản `FromISR` không bao giờ bị block, đảm bảo tính an toàn cho ngắt.</v>
       </c>
       <c r="F5" t="str">
-        <v>Vì API thường có thể gây block/delay hệ thống, làm treo tiến trình ISR; khắc phục bằng cách sử dụng các API chuyên biệt cho ngắt có hậu tố "FromISR" (như `xSemaphoreGiveFromISR()`) — tránh gây block trong ngắt sử dụng API FromISR</v>
+        <v>Khắc phục bằng cách viết code ngắt hoàn toàn bằng ngôn ngữ Assembly thay vì C nhúng — viết code Assembly</v>
       </c>
       <c r="G5" t="str">
         <v>Vì gọi API thường trong ngắt sẽ làm sập nguồn điện của vi điều khiển ngay lập tức — sập nguồn điện chip</v>
@@ -565,10 +565,10 @@
         <v>Vì ISR chỉ hỗ trợ đọc dữ liệu chứ không cho phép thực hiện bất kỳ phép toán logic nào — giới hạn tính năng ISR</v>
       </c>
       <c r="I5" t="str">
-        <v>Khắc phục bằng cách viết code ngắt hoàn toàn bằng ngôn ngữ Assembly thay vì C nhúng — viết code Assembly</v>
+        <v>Vì API thường có thể gây block/delay hệ thống, làm treo tiến trình ISR; khắc phục bằng cách sử dụng các API chuyên biệt cho ngắt có hậu tố "FromISR" (như `xSemaphoreGiveFromISR()`) — tránh gây block trong ngắt sử dụng API FromISR</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -588,7 +588,7 @@
         <v>Idle Task có priority thấp nhất (0). Khi CPU rảnh rỗi (không có việc gì làm), Idle Task sẽ chạy. Đây là nơi lý tưởng để cấu hình chip ngủ (Sleep Mode) nhằm tiết kiệm năng lượng cho các thiết bị chạy pin.</v>
       </c>
       <c r="F6" t="str">
-        <v>Là task tự động chạy khi không có task nào khác ở trạng thái Ready, thường dùng để đưa chip vào chế độ tiết kiệm năng lượng (Low-power/Sleep) — chạy khi rảnh tiết kiệm điện năng</v>
+        <v>Là task tự động xóa toàn bộ các tệp tin log rác lưu trữ trên bộ nhớ ngoài Flash — dọn dẹp bộ nhớ Flash</v>
       </c>
       <c r="G6" t="str">
         <v>Là task có độ ưu tiên cao nhất hệ thống, dùng để giám sát và tiêu diệt các task bị treo — giám sát hệ thống</v>
@@ -597,10 +597,10 @@
         <v>Là luồng xử lý riêng biệt chuyên dùng để vẽ giao diện đồ họa cho màn hình LCD — luồng đồ họa LCD</v>
       </c>
       <c r="I6" t="str">
-        <v>Là task tự động xóa toàn bộ các tệp tin log rác lưu trữ trên bộ nhớ ngoài Flash — dọn dẹp bộ nhớ Flash</v>
+        <v>Là task tự động chạy khi không có task nào khác ở trạng thái Ready, thường dùng để đưa chip vào chế độ tiết kiệm năng lượng (Low-power/Sleep) — chạy khi rảnh tiết kiệm điện năng</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -623,13 +623,13 @@
         <v>Task 1 giữ tài nguyên A và đợi tài nguyên B; Task 2 giữ tài nguyên B và đợi tài nguyên A; cả hai đều bị block vô hạn để đợi nhau — giữ tài nguyên đợi chéo lẫn nhau</v>
       </c>
       <c r="G7" t="str">
+        <v>Bộ dao động thạch anh ngoại vi của vi điều khiển bị hỏng vật lý khiến chip dừng chạy — hỏng thạch anh ngoại vi</v>
+      </c>
+      <c r="H7" t="str">
         <v>Vi điều khiển bị mất kết nối hoàn toàn với mạch nạp và không thể nạp lại code được nữa — mất kết nối mạch nạp</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>Mã nguồn chương trình C nhúng bị khai báo trùng lặp tên biến toàn cục trong nhiều file — trùng lặp tên biến</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Bộ dao động thạch anh ngoại vi của vi điều khiển bị hỏng vật lý khiến chip dừng chạy — hỏng thạch anh ngoại vi</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -652,19 +652,19 @@
         <v>Queue được cấp phát tĩnh hoặc động trong RAM dựa trên tích: Queue Length * Item Size. Cần khai báo Item Size chính xác (ví dụ `sizeof(DataStruct)`) để tránh lỗi ghi đè tràn bộ nhớ.</v>
       </c>
       <c r="F8" t="str">
+        <v>Queue Length: Độ dài tính bằng milimét của đường dây bus truyền dữ liệu — độ dài dây bus</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Item Size: Độ lớn vật lý của con chip vi điều khiển khi hàn lên bảng mạch — kích thước vật lý chip</v>
+      </c>
+      <c r="H8" t="str">
         <v>Queue Length: Số lượng phần tử tối đa hàng đợi có thể chứa; Item Size: Kích thước tính bằng byte của mỗi phần tử đó — số lượng phần tử tối đa và kích thước byte mỗi phần tử</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Queue Length: Độ dài tính bằng milimét của đường dây bus truyền dữ liệu — độ dài dây bus</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Item Size: Độ lớn vật lý của con chip vi điều khiển khi hàn lên bảng mạch — kích thước vật lý chip</v>
       </c>
       <c r="I8" t="str">
         <v>Queue Length: Tổng số lượng task đang lắng nghe hàng đợi đó cùng một lúc — số lượng task lắng nghe</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Preemptive là cơ chế lập lịch phổ biến nhất trong RTOS. Nó đảm bảo tính phản hồi nhanh của hệ thống đối với các sự kiện khẩn cấp. Khác với Cooperative Scheduling (lập lịch hợp tác, task tự nhường CPU).</v>
       </c>
       <c r="F9" t="str">
+        <v>Các task tự nguyện chia sẻ CPU bằng cách tự gọi hàm nhường quyền khi chạy xong một chu trình — chia sẻ tự nguyện hợp tác</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Hệ điều hành chia đều thời gian chạy CPU (Time-slice) cho tất cả các task bất kể độ ưu tiên của chúng — chia đều thời gian CPU</v>
+      </c>
+      <c r="H9" t="str">
+        <v>Task nào được tạo ra đầu tiên trong hàm main() sẽ được chạy liên tục cho đến khi kết thúc dự án — chạy tuần tự tạo trước</v>
+      </c>
+      <c r="I9" t="str">
         <v>Khi một task có độ ưu tiên cao hơn chuyển sang trạng thái Ready, nó sẽ lập tức ngắt (cướp quyền) task có độ ưu tiên thấp hơn đang chạy để chiếm CPU — cướp quyền CPU dựa trên độ ưu tiên</v>
       </c>
-      <c r="G9" t="str">
-        <v>Các task tự nguyện chia sẻ CPU bằng cách tự gọi hàm nhường quyền khi chạy xong một chu trình — chia sẻ tự nguyện hợp tác</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Hệ điều hành chia đều thời gian chạy CPU (Time-slice) cho tất cả các task bất kể độ ưu tiên của chúng — chia đều thời gian CPU</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Task nào được tạo ra đầu tiên trong hàm main() sẽ được chạy liên tục cho đến khi kết thúc dự án — chạy tuần tự tạo trước</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -748,19 +748,19 @@
         <v>FreeRTOS cung cấp cơ chế kiểm tra stack (Stack Overflow Detection). Khi chuyển đổi ngữ cảnh (context switch), hệ điều hành sẽ kiểm tra xem con trỏ stack của task có vượt quá giới hạn an toàn hoặc vùng đệm (watermark) được định nghĩa sẵn không. Nếu phát hiện tràn, nó sẽ gọi hàm hook để ghi log hoặc reset an toàn.</v>
       </c>
       <c r="F11" t="str">
+        <v>Chạy chương trình mô phỏng trên máy tính thông qua công cụ Proteus để quét lỗi — mô phỏng Proteus quét lỗi</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Mã hóa toàn bộ các biến cục bộ của task thành định dạng chuỗi văn bản MD5 — mã hóa biến cục bộ MD5</v>
+      </c>
+      <c r="H11" t="str">
         <v>Cấu hình hằng số `configCHECK_FOR_STACK_OVERFLOW` lớn hơn 0 và viết hàm callback `vApplicationStackOverflowHook()` để xử lý khi phát hiện tràn — cấu hình check stack overflow hook callback</v>
       </c>
-      <c r="G11" t="str">
+      <c r="I11" t="str">
         <v>Sử dụng một cầu chì vật lý hàn trên chân cấp nguồn của con chip vi điều khiển — cầu chì vật lý</v>
       </c>
-      <c r="H11" t="str">
-        <v>Mã hóa toàn bộ các biến cục bộ của task thành định dạng chuỗi văn bản MD5 — mã hóa biến cục bộ MD5</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Chạy chương trình mô phỏng trên máy tính thông qua công cụ Proteus để quét lỗi — mô phỏng Proteus quét lỗi</v>
-      </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
